--- a/part_1_table.xlsx
+++ b/part_1_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianlw/Uni/comp/elec1601/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unisydneyedu-my.sharepoint.com/personal/iwan0636_uni_sydney_edu_au/Documents/Documents/ELEC1601/cool-team-ELEC1601/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB800D23-7D27-7049-9AC4-ECAE349A5E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{BB800D23-7D27-7049-9AC4-ECAE349A5E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{587DDF9F-143E-4D91-BDC7-50FC5D6F1EE8}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{C7FD49B5-8C3C-6843-8733-786785293AE7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7FD49B5-8C3C-6843-8733-786785293AE7}"/>
   </bookViews>
   <sheets>
     <sheet name="part_1_table" sheetId="1" r:id="rId1"/>
@@ -24,16 +24,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="20">
   <si>
     <t>target distance</t>
   </si>
@@ -90,13 +91,16 @@
   </si>
   <si>
     <t>12.4344/c</t>
+  </si>
+  <si>
+    <t>1490 is equilibrium</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -951,9 +955,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CCC8453-B2ED-4F41-A9CD-F70266DAC4D5}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1.5</v>
       </c>
@@ -1011,7 +1015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1040,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>5</v>
       </c>
@@ -1072,7 +1076,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>10</v>
       </c>
@@ -1101,7 +1105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>15</v>
       </c>
@@ -1130,7 +1134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>1.5</v>
       </c>
@@ -1188,7 +1192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1217,7 +1221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1246,7 +1250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1278,7 +1282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>15</v>
       </c>
@@ -1307,7 +1311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1336,7 +1340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>1.5</v>
       </c>
@@ -1368,7 +1372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1397,7 +1401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>5</v>
       </c>
@@ -1426,7 +1430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>10</v>
       </c>
@@ -1455,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18">
       <c r="A26">
         <v>15</v>
       </c>
@@ -1484,20 +1488,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18">
       <c r="A30" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18">
       <c r="I31" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R31" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18">
       <c r="B32">
         <v>1300</v>
       </c>
@@ -1550,7 +1554,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -1606,7 +1610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1662,12 +1666,12 @@
         <v>12.4344</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18">
       <c r="A37" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18">
       <c r="I38" t="s">
         <v>13</v>
       </c>
@@ -1675,7 +1679,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18">
       <c r="B39">
         <v>1300</v>
       </c>
@@ -1728,7 +1732,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1786,7 +1790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -1859,7 +1863,7 @@
         <v>12.4344</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18">
       <c r="B44" t="s">
         <v>18</v>
       </c>

--- a/part_1_table.xlsx
+++ b/part_1_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unisydneyedu-my.sharepoint.com/personal/iwan0636_uni_sydney_edu_au/Documents/Documents/ELEC1601/cool-team-ELEC1601/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianlw/Uni/comp/elec1601/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{BB800D23-7D27-7049-9AC4-ECAE349A5E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{587DDF9F-143E-4D91-BDC7-50FC5D6F1EE8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB800D23-7D27-7049-9AC4-ECAE349A5E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7FD49B5-8C3C-6843-8733-786785293AE7}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{C7FD49B5-8C3C-6843-8733-786785293AE7}"/>
   </bookViews>
   <sheets>
     <sheet name="part_1_table" sheetId="1" r:id="rId1"/>
@@ -24,17 +24,16 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
   <si>
     <t>target distance</t>
   </si>
@@ -92,15 +91,12 @@
   <si>
     <t>12.4344/c</t>
   </si>
-  <si>
-    <t>1490 is equilibrium</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -955,9 +951,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CCC8453-B2ED-4F41-A9CD-F70266DAC4D5}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +982,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1.5</v>
       </c>
@@ -1015,7 +1011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1044,7 +1040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5</v>
       </c>
@@ -1076,7 +1072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>10</v>
       </c>
@@ -1105,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>15</v>
       </c>
@@ -1134,7 +1130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1163,7 +1159,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1.5</v>
       </c>
@@ -1192,7 +1188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1221,7 +1217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1250,7 +1246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1282,7 +1278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>15</v>
       </c>
@@ -1311,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1340,7 +1336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1.5</v>
       </c>
@@ -1372,7 +1368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1401,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>5</v>
       </c>
@@ -1430,7 +1426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>10</v>
       </c>
@@ -1459,7 +1455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>15</v>
       </c>
@@ -1488,20 +1484,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="I31" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R31" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>1300</v>
       </c>
@@ -1554,7 +1550,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -1610,7 +1606,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1666,12 +1662,12 @@
         <v>12.4344</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="I38" t="s">
         <v>13</v>
       </c>
@@ -1679,7 +1675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>1300</v>
       </c>
@@ -1732,7 +1728,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1790,7 +1786,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -1863,7 +1859,7 @@
         <v>12.4344</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>18</v>
       </c>
